--- a/Présentation/Cahier_de_recette_Inscription1.xlsx
+++ b/Présentation/Cahier_de_recette_Inscription1.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yoann.gnangla\Documents\GitHub\mini-projet2\Présentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ygnan\mini-projet2\Présentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47E45BD8-CF9F-48AE-AFB5-983FCBF74305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11343F16-F49D-4801-82EE-041B9E2A8DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BE5482E-D2AE-4F00-951B-4FE86FA21030}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{1BE5482E-D2AE-4F00-951B-4FE86FA21030}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
     <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
+    <sheet name="Feuil4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
   <si>
     <t>titre:</t>
   </si>
@@ -110,6 +111,22 @@
   </si>
   <si>
     <t>Cliquer sur " + "</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajouter un contact </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Envoyer un message et créer un groupe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajouter un contact et création de groupe </t>
+  </si>
+  <si>
+    <t>Cliquer sur 
+le nom de votre contact</t>
+  </si>
+  <si>
+    <t>Ouverture du la discussion avec votre contact</t>
   </si>
 </sst>
 </file>
@@ -153,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -164,6 +181,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -500,14 +520,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6358CC9-4BFE-4BD3-AA6F-00FCC90E5182}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="41.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="41.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -515,7 +535,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -523,12 +543,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -542,7 +562,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>1</v>
       </c>
@@ -553,7 +573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="96" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2</v>
       </c>
@@ -561,7 +581,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -572,7 +592,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4</v>
       </c>
@@ -580,7 +600,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>5</v>
       </c>
@@ -599,15 +619,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4FD4750-82D2-430A-A762-CA2C23A5ED33}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -623,12 +643,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -642,7 +662,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -650,7 +670,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -661,7 +681,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
     </row>
   </sheetData>
@@ -671,21 +691,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80953212-7680-4581-A57E-E6C4C2616894}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -693,12 +715,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -712,7 +734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -720,15 +742,92 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="9" spans="1:4" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95250FE3-3227-4105-8EAA-5CDEBE2771A7}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
       <c r="D8" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Présentation/Cahier_de_recette_Inscription1.xlsx
+++ b/Présentation/Cahier_de_recette_Inscription1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ygnan\mini-projet2\Présentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11343F16-F49D-4801-82EE-041B9E2A8DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3A114E-67F1-4E10-A2A3-0F59A2A10C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{1BE5482E-D2AE-4F00-951B-4FE86FA21030}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="29">
   <si>
     <t>titre:</t>
   </si>
@@ -127,6 +127,12 @@
   </si>
   <si>
     <t>Ouverture du la discussion avec votre contact</t>
+  </si>
+  <si>
+    <t>Ecrire un message puis l'envoyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Envoie de votre message </t>
   </si>
 </sst>
 </file>
@@ -170,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -184,6 +190,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -691,7 +700,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80953212-7680-4581-A57E-E6C4C2616894}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.5546875" customWidth="1"/>
@@ -757,8 +766,39 @@
       <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="6" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Présentation/Cahier_de_recette_Inscription1.xlsx
+++ b/Présentation/Cahier_de_recette_Inscription1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ygnan\mini-projet2\Présentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3A114E-67F1-4E10-A2A3-0F59A2A10C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32C358DB-AF53-4510-B72D-DD8E900F1323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{1BE5482E-D2AE-4F00-951B-4FE86FA21030}"/>
   </bookViews>

--- a/Présentation/Cahier_de_recette_Inscription1.xlsx
+++ b/Présentation/Cahier_de_recette_Inscription1.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ygnan\mini-projet2\Présentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32C358DB-AF53-4510-B72D-DD8E900F1323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2E1D25-5A83-4BB0-A3D6-02DA4D2C0510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{1BE5482E-D2AE-4F00-951B-4FE86FA21030}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1BE5482E-D2AE-4F00-951B-4FE86FA21030}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
     <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
-    <sheet name="Feuil4" sheetId="4" r:id="rId4"/>
+    <sheet name="Feuil4" sheetId="5" r:id="rId4"/>
+    <sheet name="Feuil5" sheetId="4" r:id="rId5"/>
+    <sheet name="Feuil6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
   <si>
     <t>titre:</t>
   </si>
@@ -72,9 +74,6 @@
 - Confirmer le mot de passe</t>
   </si>
   <si>
-    <t>Cliquer sur "S'inscrire"</t>
-  </si>
-  <si>
     <t>vous emmene sur la page d'inscription</t>
   </si>
   <si>
@@ -86,9 +85,6 @@
 - Mot de passe </t>
   </si>
   <si>
-    <t>Cliquer sur "Se connecter"</t>
-  </si>
-  <si>
     <t>renvoie vers la page de discussion</t>
   </si>
   <si>
@@ -104,35 +100,97 @@
     <t xml:space="preserve">iniatialisation: Lancer l'application et avoir déjà un compte </t>
   </si>
   <si>
-    <t>Ajouter un contact</t>
-  </si>
-  <si>
     <t>Ecrire le nom d'utilisateur d'un contact</t>
   </si>
   <si>
-    <t>Cliquer sur " + "</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajouter un contact </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Envoyer un message et créer un groupe </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajouter un contact et création de groupe </t>
-  </si>
-  <si>
-    <t>Cliquer sur 
+    <t>Ouverture du la discussion avec votre contact</t>
+  </si>
+  <si>
+    <t>Ecrire un message puis l'envoyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Envoie de votre message </t>
+  </si>
+  <si>
+    <t>Le nom de votre contact change de couleur et passe en bleu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Création d'un groupe</t>
+  </si>
+  <si>
+    <t>Procedure de test : accepter contact  et création de groupe</t>
+  </si>
+  <si>
+    <t>accepter contact  et création de groupe</t>
+  </si>
+  <si>
+    <t>Notification d'une demande de contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Votre contact doit, au préalable, vous avoir ajouté( fait une demande d'amie). </t>
+  </si>
+  <si>
+    <t>Ajouter un contact, envoyer un message et image</t>
+  </si>
+  <si>
+    <t>envoie d'image, cliquez sur"image"</t>
+  </si>
+  <si>
+    <t>Ouverture de votre explorateur de fchiers</t>
+  </si>
+  <si>
+    <t>Choisir une image et ensuite cliquez sur "Envoyer"</t>
+  </si>
+  <si>
+    <t>Envoie de votre image a votre destinataire</t>
+  </si>
+  <si>
+    <t>Cliquez sur 
 le nom de votre contact</t>
   </si>
   <si>
-    <t>Ouverture du la discussion avec votre contact</t>
-  </si>
-  <si>
-    <t>Ecrire un message puis l'envoyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Envoie de votre message </t>
+    <t>Cliquez sur " + "</t>
+  </si>
+  <si>
+    <t>Cliquez sur "Se connecter"</t>
+  </si>
+  <si>
+    <t>Cliquez sur "S'inscrire"</t>
+  </si>
+  <si>
+    <t>Ajout et envoie</t>
+  </si>
+  <si>
+    <t>Cliquez sur le "+" pour ajouter votre contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecrire dans"Ajouter Groupe".
+un nom de groupe
+Puis cliquez sur le"+" </t>
+  </si>
+  <si>
+    <t>Rejoindre un groupe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedure de test : Rejoindre un groupe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Votre contact doit, au préalable, avoir crée un groupe. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intégration dans le groupe </t>
+  </si>
+  <si>
+    <t>Se deconnecter</t>
+  </si>
+  <si>
+    <t>Procedure de test : Deconnexion</t>
+  </si>
+  <si>
+    <t>Cliquez sur le bouton "deconnexion"</t>
+  </si>
+  <si>
+    <t>Redirection vers la page de connexion</t>
   </si>
 </sst>
 </file>
@@ -176,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -193,6 +251,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -541,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -572,18 +636,18 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="9" spans="1:4" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="8">
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -591,33 +655,33 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="8">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>4</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11" s="4" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -641,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -649,12 +713,12 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -672,22 +736,22 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="8">
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -703,8 +767,8 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="25.21875" customWidth="1"/>
     <col min="4" max="4" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -713,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -721,12 +785,12 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>18</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -744,62 +808,70 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="8">
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>3</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>5</v>
+      <c r="D11" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="A12" s="8">
         <v>6</v>
       </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>7</v>
-      </c>
+      <c r="A13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>8</v>
-      </c>
+      <c r="A14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -807,29 +879,31 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95250FE3-3227-4105-8EAA-5CDEBE2771A7}">
-  <dimension ref="A1:D9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CBDFC4E-A40F-4CE7-B5D8-C62947BDAB74}">
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>18</v>
+      <c r="A5" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -846,29 +920,178 @@
         <v>6</v>
       </c>
     </row>
+    <row r="7" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>4</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95250FE3-3227-4105-8EAA-5CDEBE2771A7}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="8">
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="5"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484531BA-5BF8-4E75-95F4-46A42AA46BAF}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>3</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="7"/>
+      <c r="D8" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Présentation/Cahier_de_recette_Inscription1.xlsx
+++ b/Présentation/Cahier_de_recette_Inscription1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ygnan\mini-projet2\Présentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brando.colamarco\Documents\GitHub\mini-projet2\Présentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2E1D25-5A83-4BB0-A3D6-02DA4D2C0510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE6D5C7-FD32-44FA-8C7D-D7873A188658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1BE5482E-D2AE-4F00-951B-4FE86FA21030}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{1BE5482E-D2AE-4F00-951B-4FE86FA21030}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="53">
   <si>
     <t>titre:</t>
   </si>
@@ -65,19 +65,6 @@
   </si>
   <si>
     <t>Inscription</t>
-  </si>
-  <si>
-    <t>Remplir tous les champs
-- Nom utlisateur
-- Email valide ( contenant un @ par defaut )
-- Mot de passe ( 8 caractères minimum, 1 majuscule, 1 chiffre, 1 caractère spécial
-- Confirmer le mot de passe</t>
-  </si>
-  <si>
-    <t>vous emmene sur la page d'inscription</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vous emmene sur la page de connexion </t>
   </si>
   <si>
     <t xml:space="preserve">Remplir tous les champs
@@ -118,12 +105,6 @@
     <t xml:space="preserve"> Création d'un groupe</t>
   </si>
   <si>
-    <t>Procedure de test : accepter contact  et création de groupe</t>
-  </si>
-  <si>
-    <t>accepter contact  et création de groupe</t>
-  </si>
-  <si>
     <t>Notification d'une demande de contact</t>
   </si>
   <si>
@@ -136,13 +117,7 @@
     <t>envoie d'image, cliquez sur"image"</t>
   </si>
   <si>
-    <t>Ouverture de votre explorateur de fchiers</t>
-  </si>
-  <si>
     <t>Choisir une image et ensuite cliquez sur "Envoyer"</t>
-  </si>
-  <si>
-    <t>Envoie de votre image a votre destinataire</t>
   </si>
   <si>
     <t>Cliquez sur 
@@ -172,25 +147,70 @@
     <t>Rejoindre un groupe</t>
   </si>
   <si>
-    <t xml:space="preserve">Procedure de test : Rejoindre un groupe </t>
-  </si>
-  <si>
     <t xml:space="preserve">Votre contact doit, au préalable, avoir crée un groupe. </t>
   </si>
   <si>
     <t xml:space="preserve">Intégration dans le groupe </t>
   </si>
   <si>
-    <t>Se deconnecter</t>
-  </si>
-  <si>
-    <t>Procedure de test : Deconnexion</t>
-  </si>
-  <si>
-    <t>Cliquez sur le bouton "deconnexion"</t>
-  </si>
-  <si>
     <t>Redirection vers la page de connexion</t>
+  </si>
+  <si>
+    <t>OK?</t>
+  </si>
+  <si>
+    <t>Remplir tous les champs
+- Nom utlisateur
+- Email valide ( contenant un @ par défaut )
+- Mot de passe ( 8 caractères minimum, 1 majuscule, 1 chiffre, 1 caractère spécial
+- Confirmer le mot de passe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remplir tous les champs
+- Nom d'utlisateur
+- Mot de passe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous emmène sur la page de connexion </t>
+  </si>
+  <si>
+    <t>vous emmène sur la page d'inscription</t>
+  </si>
+  <si>
+    <t>Vous renvoie vers la page de discussion</t>
+  </si>
+  <si>
+    <t>Cliquez sur le bouton "Deconnéxion"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iniatialisation: Lancer l'application et avoir déjà un compte </t>
+  </si>
+  <si>
+    <t>Procedure de test : Déconnexion</t>
+  </si>
+  <si>
+    <t>Titre :</t>
+  </si>
+  <si>
+    <t>Se déconnecter</t>
+  </si>
+  <si>
+    <t>Titre:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procédure de test : Rejoindre un groupe </t>
+  </si>
+  <si>
+    <t>Ouverture de votre explorateur de fichiers</t>
+  </si>
+  <si>
+    <t>Envoi de votre image a votre destinataire</t>
+  </si>
+  <si>
+    <t>Accepter contact  et création de groupe</t>
+  </si>
+  <si>
+    <t>Procédure de test : accepter contact  et création de groupe</t>
   </si>
 </sst>
 </file>
@@ -222,7 +242,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -230,18 +250,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -255,9 +286,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -592,170 +647,250 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6358CC9-4BFE-4BD3-AA6F-00FCC90E5182}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="41.44140625" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="41.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="E7" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
         <v>1</v>
       </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="B8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="B9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
         <v>3</v>
       </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="B10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
         <v>4</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="B11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
         <v>5</v>
       </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
+      <c r="B12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4FD4750-82D2-430A-A762-CA2C23A5ED33}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="E6" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="B7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
         <v>2</v>
       </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="4"/>
+      <c r="B8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -764,114 +899,155 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80953212-7680-4581-A57E-E6C4C2616894}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="25.21875" customWidth="1"/>
-    <col min="4" max="4" width="38.33203125" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="4" max="4" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" spans="1:5" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+    <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
         <v>5</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
-        <v>3</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
+      <c r="B12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -880,83 +1056,122 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CBDFC4E-A40F-4CE7-B5D8-C62947BDAB74}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="53" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="16"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="E6" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="B7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
         <v>2</v>
       </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="B9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
         <v>4</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="B10" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -965,71 +1180,106 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95250FE3-3227-4105-8EAA-5CDEBE2771A7}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="16"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="E6" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="B7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
         <v>2</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="5"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
+      <c r="B8" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="3"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1038,60 +1288,92 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484531BA-5BF8-4E75-95F4-46A42AA46BAF}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="35" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="16"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="E6" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="7"/>
-      <c r="D8" s="6"/>
+      <c r="B7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="5"/>
+      <c r="D8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
